--- a/inspection_forms/034_site_visit_form--inspection_forms.xlsx
+++ b/inspection_forms/034_site_visit_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>site_visit_form_page_1</t>
+          <t>contact_information_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Site Visit</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>site_visit_form_page_2</t>
+          <t>contact_information_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Name (Confirmation)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>site_visit_form_page_3</t>
+          <t>contact_information_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_details_1</t>
+          <t>contact_information_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Email (Confirmation)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,64 +612,64 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_details_2</t>
+          <t>contact_information_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone (Mobile or Landline)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>contact_details_3</t>
+          <t>site_inspection_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Checklist 1 (Select Multiple)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4</t>
+          <t>site_inspection_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Site Visit</t>
+          <t>Checkboxes 1-5 (Select Multiple)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_1</t>
+          <t>site_inspection_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Checklist 1</t>
+          <t>Checkboxes 6-10 (Select Multiple)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,64 +704,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_2</t>
+          <t>site_inspection_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Checkboxes 1-5</t>
+          <t>Checkboxes 11-15 (Select Multiple)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_3</t>
+          <t>site_inspection_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Checkboxes 6-10</t>
+          <t>Site Visit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_4</t>
+          <t>site_inspection_6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Checkboxes 11-15</t>
+          <t>Site Inspection 6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>site_visit_form_page_5</t>
+          <t>site_inspection_7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Site Visit</t>
+          <t>Site Inspection 7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>site_visit_form_page_6</t>
+          <t>additional_information_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -806,6 +806,121 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>additional_information_2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Additional Information 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>site_inspection_8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Checklists 16-20 (Select Multiple)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>site_visit_form_page_6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>site_visit_form_page_7</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Site Visit Form Page 7</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>site_visit_form_page_8</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Site Visit Form Page 8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,306 +965,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_1_choices</t>
+          <t>site_inspection_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>checklist_1_option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Checklist 1 Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_1_choices</t>
+          <t>site_inspection_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>checklist_1_option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Checklist 1 Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_1_choices</t>
+          <t>site_inspection_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>checklist_1_option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Checklist 1 Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_2_choices</t>
+          <t>site_inspection_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>checkboxes_1-5_option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Checkboxes 1-5 Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_2_choices</t>
+          <t>site_inspection_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>checkboxes_1-5_option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Checkboxes 1-5 Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_2_choices</t>
+          <t>site_inspection_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>checkboxes_1-5_option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Checkboxes 1-5 Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_2_choices</t>
+          <t>site_inspection_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>checkboxes_1-5_option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Checkboxes 1-5 Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_2_choices</t>
+          <t>site_inspection_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>checkboxes_1-5_option_5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Checkboxes 1-5 Option 5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_3_choices</t>
+          <t>site_inspection_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>checkboxes_6-10_option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Checkboxes 6-10 Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_3_choices</t>
+          <t>site_inspection_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>checkboxes_6-10_option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Checkboxes 6-10 Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_3_choices</t>
+          <t>site_inspection_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>checkboxes_6-10_option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Checkboxes 6-10 Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_3_choices</t>
+          <t>site_inspection_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>checkboxes_6-10_option_4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Checkboxes 6-10 Option 4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_3_choices</t>
+          <t>site_inspection_8_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>checkboxes_6-10_option_5</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Checkboxes 6-10 Option 5</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_4_choices</t>
+          <t>site_inspection_8_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>checkboxes_11-15_option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Checkboxes 11-15 Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>site_visit_form_page_4_4_choices</t>
+          <t>site_inspection_8_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>checkboxes_11-15_option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Checkboxes 11-15 Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>site_visit_form_page_4_4_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>checkboxes_11-15_option_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Checkboxes 11-15 Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>site_visit_form_page_4_4_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>checkboxes_11-15_option_4</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Checkboxes 11-15 Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>site_visit_form_page_4_4_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>checkboxes_11-15_option_5</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Checkboxes 11-15 Option 5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
